--- a/kod-emails-login.xlsx
+++ b/kod-emails-login.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\ariston\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AA3D70B-2223-4887-B467-F20B7E26DB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{849AF611-923E-4227-B714-C25B4BAC5073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9039C704-6E2C-4F70-B608-20534BC25C5C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>ΚΩΔΙΚΟΙ ARISTON WASH &amp; DRY</t>
   </si>
@@ -52,6 +52,30 @@
   </si>
   <si>
     <t>admin@admin.gr</t>
+  </si>
+  <si>
+    <t>08021975Mmm</t>
+  </si>
+  <si>
+    <t>M8275K3975</t>
+  </si>
+  <si>
+    <t>karpaM8275K3975</t>
+  </si>
+  <si>
+    <t>suM8275K3975</t>
+  </si>
+  <si>
+    <t>coM8275K3975</t>
+  </si>
+  <si>
+    <t>teM8275K3975</t>
+  </si>
+  <si>
+    <t>e33459kmge</t>
+  </si>
+  <si>
+    <t>?vcYbHAPn51I$D1H*^mA</t>
   </si>
 </sst>
 </file>
@@ -428,55 +452,85 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0CE70F7-CB85-4638-AAD6-C9B560DD03C5}">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
